--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536317_LIGAREGULARB_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536317_LIGAREGULARB_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y29"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,7 +878,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X. TORRENT BAYÉ</t>
+          <t>P. SALA VALLMAJO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,40 +890,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2918</v>
+        <v>-0.6049</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2918</v>
+        <v>-0.0636</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0.5414</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2918</v>
+        <v>-0.4471</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2918</v>
+        <v>-0.1945</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.2526</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2918</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2918</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.4471</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.1945</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.2526</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -935,13 +935,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.0636</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. SALA VALLMAJO</t>
+          <t>O. FUENTES PELUFO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -973,67 +973,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6049</v>
+        <v>-0.9179</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0636</v>
+        <v>-1.4654</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5414</v>
+        <v>0.5475</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4471</v>
+        <v>-2.6312</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1945</v>
+        <v>-1.5265</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2526</v>
+        <v>-1.1047</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-1.6311</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.2909</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.3402</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4471</v>
+        <v>-1.0001</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1945</v>
+        <v>-1.2356</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2526</v>
+        <v>0.2356</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.8493</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.2055</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.0548</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1578</v>
+        <v>-0.258</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0636</v>
+        <v>0.1315</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.3895</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1219</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2397</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1178</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. FUENTES PELUFO</t>
+          <t>J. LEEROY OSAGIE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1056,67 +1056,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9179</v>
+        <v>-1.2451</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4654</v>
+        <v>-1.7033</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5475</v>
+        <v>0.4582</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.6312</v>
+        <v>-1.7156</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5265</v>
+        <v>-2.5747</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1047</v>
+        <v>0.8591</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6311</v>
+        <v>-1.3101</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2909</v>
+        <v>-1.4284</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3402</v>
+        <v>0.1184</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0001</v>
+        <v>-0.4055</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2356</v>
+        <v>-1.1463</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2356</v>
+        <v>0.7408</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8493</v>
+        <v>1.6439</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.2055</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0548</v>
+        <v>1.8493</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.258</v>
+        <v>-0.5762</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1315</v>
+        <v>-0.1878</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3895</v>
+        <v>-0.3884</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1219</v>
+        <v>-0.5972</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2397</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1178</v>
+        <v>-0.5972</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. LEEROY OSAGIE</t>
+          <t>B. SAGNA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,67 +1139,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2451</v>
+        <v>-1.8245</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7033</v>
+        <v>-4.2114</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4582</v>
+        <v>2.3869</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7156</v>
+        <v>-2.186</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.5747</v>
+        <v>-2.9032</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8591</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3101</v>
+        <v>-2.4374</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.4284</v>
+        <v>-1.8462</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1184</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4055</v>
+        <v>0.2514</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1463</v>
+        <v>-1.057</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7408</v>
+        <v>1.3084</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6439</v>
+        <v>0.8219</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2055</v>
+        <v>-1.2329</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8493</v>
+        <v>2.0548</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5762</v>
+        <v>-1.1509</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1878</v>
+        <v>-0.5411</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3884</v>
+        <v>-0.6097</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5972</v>
+        <v>0.6904</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5972</v>
+        <v>0.6904</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. SAGNA</t>
+          <t>A. DOMINGUEZ ESPELT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1222,67 +1222,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8245</v>
+        <v>-1.9114</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2114</v>
+        <v>-2.9833</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3869</v>
+        <v>1.0719</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.186</v>
+        <v>-1.9163</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.9032</v>
+        <v>-1.4205</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7171999999999999</v>
+        <v>-0.4958</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.4374</v>
+        <v>-1.5261</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.8462</v>
+        <v>0.1675</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5911999999999999</v>
+        <v>-1.6936</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2514</v>
+        <v>-0.3902</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.057</v>
+        <v>-1.588</v>
       </c>
       <c r="O10" t="n">
-        <v>1.3084</v>
+        <v>1.1977</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8219</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.2329</v>
+        <v>-2.0548</v>
       </c>
       <c r="R10" t="n">
         <v>2.0548</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1509</v>
+        <v>-0.4745</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5411</v>
+        <v>0.1182</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6097</v>
+        <v>-0.5927</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6904</v>
+        <v>0.4794</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.4794</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6904</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ ESPELT</t>
+          <t>X. TORRENT BAYE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,67 +1305,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9114</v>
+        <v>-2.4563</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9833</v>
+        <v>-1.7054</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0719</v>
+        <v>-0.7509</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.9163</v>
+        <v>-2.9224</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4205</v>
+        <v>-0.4381</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4958</v>
+        <v>-2.4843</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5261</v>
+        <v>-1.6018</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1675</v>
+        <v>0.4085</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.6936</v>
+        <v>-2.0103</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3902</v>
+        <v>-1.3206</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.588</v>
+        <v>-0.8466</v>
       </c>
       <c r="O11" t="n">
-        <v>1.1977</v>
+        <v>-0.474</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0548</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0548</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4745</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1182</v>
+        <v>-0.1035</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5927</v>
+        <v>0.1929</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4794</v>
+        <v>-0.2397</v>
       </c>
       <c r="W11" t="n">
-        <v>0.4794</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.2397</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X. TORRENT BAYE</t>
+          <t>M. MUKENDI MUKENDI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1388,58 +1388,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.748</v>
+        <v>-3.9127</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9971</v>
+        <v>-3.9196</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7509</v>
+        <v>0.0069</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.2142</v>
+        <v>-2.5147</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7299</v>
+        <v>-2.3723</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.4843</v>
+        <v>-0.1425</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8936</v>
+        <v>-2.0303</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1167</v>
+        <v>-2.1092</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.0103</v>
+        <v>0.0789</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.3206</v>
+        <v>-0.4844</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8466</v>
+        <v>-0.263</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.474</v>
+        <v>-0.2214</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6163999999999999</v>
+        <v>-1.4384</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.0548</v>
       </c>
       <c r="R12" t="n">
         <v>0.6163999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.2801</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1035</v>
+        <v>0.1655</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1929</v>
+        <v>0.1146</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2397</v>
@@ -1459,7 +1459,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. MUKENDI MUKENDI</t>
+          <t>M. RAGSDALE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1471,67 +1471,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.9127</v>
+        <v>-3.9955</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.9196</v>
+        <v>-4.6602</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0069</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.5147</v>
+        <v>-0.2378</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.3723</v>
+        <v>-2.4306</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1425</v>
+        <v>2.1928</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.0303</v>
+        <v>0.1738</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.1092</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0789</v>
+        <v>1.1058</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4844</v>
+        <v>-0.4116</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.263</v>
+        <v>-1.4987</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2214</v>
+        <v>1.087</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.4384</v>
+        <v>-1.8493</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0548</v>
+        <v>-4.1096</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6163999999999999</v>
+        <v>2.2603</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2801</v>
+        <v>-0.7302999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1655</v>
+        <v>-0.7244</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1146</v>
+        <v>-0.0058</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2397</v>
+        <v>-1.1781</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2397</v>
+        <v>-1.1781</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. RAGSDALE</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1554,157 +1554,157 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.9955</v>
+        <v>-9.583400000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.6602</v>
+        <v>-16.4471</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6647999999999999</v>
+        <v>6.864</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2378</v>
+        <v>-11.2215</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.4306</v>
+        <v>-15.3228</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1928</v>
+        <v>4.1012</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1738</v>
+        <v>-4.796199999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-3.8596</v>
       </c>
       <c r="L14" t="n">
-        <v>1.1058</v>
+        <v>-0.9365000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4116</v>
+        <v>-6.4252</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4987</v>
+        <v>-11.4632</v>
       </c>
       <c r="O14" t="n">
-        <v>1.087</v>
+        <v>5.0378</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.8493</v>
+        <v>5.137</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.1096</v>
+        <v>-12.3289</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2603</v>
+        <v>17.4658</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7302999999999999</v>
+        <v>-3.718</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7244</v>
+        <v>-2.048</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0058</v>
+        <v>-1.6699</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.1781</v>
+        <v>0.2192000000000003</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.726</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.1781</v>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>play_by_play_2536317_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
+        <v>-2.5067</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>K. BAOKO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SOL GIRONÈS BISBAL BÀSQUET</t>
+          <t>AMICS CASTELLÓ</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-9.583300000000001</v>
+        <v>5.9021</v>
       </c>
       <c r="E15" t="n">
-        <v>-16.447</v>
+        <v>3.0963</v>
       </c>
       <c r="F15" t="n">
-        <v>6.864</v>
+        <v>2.8058</v>
       </c>
       <c r="G15" t="n">
-        <v>-11.2215</v>
+        <v>7.8848</v>
       </c>
       <c r="H15" t="n">
-        <v>-15.3228</v>
+        <v>8.2569</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1012</v>
+        <v>-0.3721</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.796199999999999</v>
+        <v>7.0142</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.8596</v>
+        <v>6.9748</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.9365000000000001</v>
+        <v>0.0395</v>
       </c>
       <c r="M15" t="n">
-        <v>-6.4252</v>
+        <v>0.8705000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-11.4632</v>
+        <v>1.2821</v>
       </c>
       <c r="O15" t="n">
-        <v>5.0378</v>
+        <v>-0.4116</v>
       </c>
       <c r="P15" t="n">
-        <v>5.137</v>
+        <v>-2.6713</v>
       </c>
       <c r="Q15" t="n">
-        <v>-12.3289</v>
+        <v>-4.5206</v>
       </c>
       <c r="R15" t="n">
-        <v>17.4658</v>
+        <v>1.8493</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.718</v>
+        <v>1.1475</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.048</v>
+        <v>0.8218</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.6699</v>
+        <v>0.3257</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2192000000000003</v>
+        <v>-0.4589</v>
       </c>
       <c r="W15" t="n">
-        <v>2.726</v>
+        <v>-0.2192</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.5067</v>
-      </c>
-      <c r="Y15" t="inlineStr"/>
+        <v>-0.2397</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2536317_LIGAREGULARB_PROCESSED.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. BAOKO</t>
+          <t>R. DIAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,67 +1716,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.6103</v>
+        <v>4.4472</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8045</v>
+        <v>3.1885</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8058</v>
+        <v>1.2587</v>
       </c>
       <c r="G16" t="n">
-        <v>7.593</v>
+        <v>3.2016</v>
       </c>
       <c r="H16" t="n">
-        <v>7.9651</v>
+        <v>0.6455</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3721</v>
+        <v>2.5561</v>
       </c>
       <c r="J16" t="n">
-        <v>6.7225</v>
+        <v>3.3233</v>
       </c>
       <c r="K16" t="n">
-        <v>6.683</v>
+        <v>1.5079</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0395</v>
+        <v>1.8154</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8705000000000001</v>
+        <v>-0.1217</v>
       </c>
       <c r="N16" t="n">
-        <v>1.2821</v>
+        <v>-0.8625</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4116</v>
+        <v>0.7408</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.6713</v>
+        <v>1.0274</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.5206</v>
+        <v>-0.2055</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8493</v>
+        <v>1.2329</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1475</v>
+        <v>0.3278</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8218</v>
+        <v>0.1803</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3257</v>
+        <v>0.1475</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.4589</v>
+        <v>-0.1096</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.2192</v>
+        <v>-0.1096</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2397</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. DIAZ DEL VALLE</t>
+          <t>F. STUTZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.5637</v>
+        <v>2.4008</v>
       </c>
       <c r="E18" t="n">
-        <v>2.305</v>
+        <v>-0.3244</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2587</v>
+        <v>2.7253</v>
       </c>
       <c r="G18" t="n">
-        <v>2.318</v>
+        <v>0.4712</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3537</v>
+        <v>0.7074</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9644</v>
+        <v>-0.2361</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4398</v>
+        <v>-0.5571</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2162</v>
+        <v>-0.8745000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2236</v>
+        <v>0.3173</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1217</v>
+        <v>1.0284</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8625</v>
+        <v>1.5818</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7408</v>
+        <v>-0.5535</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0274</v>
+        <v>1.2329</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2055</v>
+        <v>-0.411</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2329</v>
+        <v>1.6439</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3278</v>
+        <v>0.3474</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1803</v>
+        <v>0.0546</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1475</v>
+        <v>0.2928</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1096</v>
+        <v>0.3493</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.1096</v>
+        <v>0.589</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2397</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. STUTZ</t>
+          <t>H. ARBOSA ROLDAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4008</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3244</v>
+        <v>-3.0184</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7253</v>
+        <v>3.6741</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4712</v>
+        <v>0.9246</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7074</v>
+        <v>3.2441</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2361</v>
+        <v>-2.3194</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5571</v>
+        <v>-0.0352</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8745000000000001</v>
+        <v>2.0146</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3173</v>
+        <v>-2.0498</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0284</v>
+        <v>0.9599</v>
       </c>
       <c r="N19" t="n">
-        <v>1.5818</v>
+        <v>1.2295</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5535</v>
+        <v>-0.2696</v>
       </c>
       <c r="P19" t="n">
-        <v>1.2329</v>
+        <v>-2.4658</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.411</v>
+        <v>-4.5206</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6439</v>
+        <v>2.0548</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3474</v>
+        <v>0.7791</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0546</v>
+        <v>0.1197</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2928</v>
+        <v>0.6594</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3493</v>
+        <v>1.4178</v>
       </c>
       <c r="W19" t="n">
-        <v>0.589</v>
+        <v>1.4178</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2397</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. DÍAZ DEL VALLE</t>
+          <t>G. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,64 +2048,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.5639</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8836000000000001</v>
+        <v>-0.4159</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.9798</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.8079</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2918</v>
+        <v>-0.0513</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5918</v>
+        <v>0.8591</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.877</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2918</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5918</v>
+        <v>0.1184</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-0.8099</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>0.7408</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-1.2329</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.0548</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.8219</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.3999</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.1729</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.227</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.589</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.589</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>H. ARBOSA ROLDAN</t>
+          <t>D. LOZANO GIMENEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,64 +2131,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.229</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0184</v>
+        <v>0.0395</v>
       </c>
       <c r="F21" t="n">
-        <v>3.6741</v>
+        <v>0.1896</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9246</v>
+        <v>0.1814</v>
       </c>
       <c r="H21" t="n">
-        <v>3.2441</v>
+        <v>0.1419</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3194</v>
+        <v>0.0395</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0352</v>
+        <v>0.0395</v>
       </c>
       <c r="K21" t="n">
-        <v>2.0146</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.0498</v>
+        <v>0.0395</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9599</v>
+        <v>0.1419</v>
       </c>
       <c r="N21" t="n">
-        <v>1.2295</v>
+        <v>0.1419</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2696</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.4658</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.5206</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0548</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7791</v>
+        <v>0.0477</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1197</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6594</v>
+        <v>0.0477</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4178</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4178</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. IGLESIAS FERNANDEZ</t>
+          <t>J. GASCON TORNE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5639</v>
+        <v>-0.6826</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4159</v>
+        <v>-1.1109</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9798</v>
+        <v>0.4283</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8079</v>
+        <v>-1.4591</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0513</v>
+        <v>-1.0893</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8591</v>
+        <v>-0.3698</v>
       </c>
       <c r="J22" t="n">
-        <v>0.877</v>
+        <v>-1.4585</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7586000000000001</v>
+        <v>-0.6318</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1184</v>
+        <v>-0.8268</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.06909999999999999</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8099</v>
+        <v>-0.4575</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7408</v>
+        <v>0.457</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.2329</v>
+        <v>0.411</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.0548</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8219</v>
+        <v>0.411</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3999</v>
+        <v>0.3655</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1729</v>
+        <v>0.1079</v>
       </c>
       <c r="U22" t="n">
-        <v>0.227</v>
+        <v>0.2576</v>
       </c>
       <c r="V22" t="n">
-        <v>0.589</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.589</v>
+        <v>0.2397</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.2397</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K.  BAOKO</t>
+          <t>D. BAH</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2918</v>
+        <v>-0.868</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2918</v>
+        <v>-0.0796</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>-0.7884</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2918</v>
+        <v>2.0832</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2918</v>
+        <v>0.7348</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1.3485</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2918</v>
+        <v>1.9945</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2918</v>
+        <v>1.2449</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.7496</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>0.0887</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>-0.5102</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>0.5989</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-1.4384</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.0548</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>0.2543</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>-0.0192</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>0.2735</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.7671</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.7671</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. LOZANO GIMENEZ</t>
+          <t>G. MULERO MALDONADO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,58 +2380,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.229</v>
+        <v>-1.593</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0395</v>
+        <v>-4.3886</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1896</v>
+        <v>2.7957</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1814</v>
+        <v>-2.1739</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1419</v>
+        <v>2.061</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0395</v>
+        <v>-4.235</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0395</v>
+        <v>-3.5075</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>0.7104</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0395</v>
+        <v>-4.2179</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1419</v>
+        <v>1.3336</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1419</v>
+        <v>1.3506</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>-0.017</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>0.2055</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1.2329</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.4384</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0477</v>
+        <v>0.3755</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>0.3518</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0477</v>
+        <v>0.0237</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2451,7 +2451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. GASCON TORNE</t>
+          <t>D. CEBOLLA PORCAR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2463,64 +2463,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6826</v>
+        <v>-4.1001</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.1109</v>
+        <v>-5.9733</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4283</v>
+        <v>1.8732</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.4591</v>
+        <v>-3.2402</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.0893</v>
+        <v>-0.1406</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3698</v>
+        <v>-3.0997</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.4585</v>
+        <v>-3.6538</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6318</v>
+        <v>-0.855</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.8268</v>
+        <v>-2.7988</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.4136</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4575</v>
+        <v>0.7145</v>
       </c>
       <c r="O25" t="n">
-        <v>0.457</v>
+        <v>-0.3009</v>
       </c>
       <c r="P25" t="n">
-        <v>0.411</v>
+        <v>-1.0274</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-2.2603</v>
       </c>
       <c r="R25" t="n">
-        <v>0.411</v>
+        <v>1.2329</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3655</v>
+        <v>0.4073</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1079</v>
+        <v>-0.0592</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2576</v>
+        <v>0.4665</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-0.2397</v>
       </c>
       <c r="W25" t="n">
-        <v>0.2397</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>-0.2397</v>
@@ -2534,7 +2534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>D. BAH</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2546,318 +2546,69 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.868</v>
+        <v>10.6106</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0796</v>
+        <v>-6.863900000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.7884</v>
+        <v>17.4748</v>
       </c>
       <c r="G26" t="n">
-        <v>2.0832</v>
+        <v>11.2217</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7348</v>
+        <v>15.323</v>
       </c>
       <c r="I26" t="n">
-        <v>1.3485</v>
+        <v>-4.1013</v>
       </c>
       <c r="J26" t="n">
-        <v>1.9945</v>
+        <v>6.4255</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2449</v>
+        <v>11.4631</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7496</v>
+        <v>-5.037699999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0887</v>
+        <v>4.796399999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.5102</v>
+        <v>3.8597</v>
       </c>
       <c r="O26" t="n">
-        <v>0.5989</v>
+        <v>0.9366000000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.4384</v>
+        <v>-5.1371</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.0548</v>
+        <v>-17.466</v>
       </c>
       <c r="R26" t="n">
-        <v>0.6163999999999999</v>
+        <v>12.3289</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2543</v>
+        <v>4.7454</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0192</v>
+        <v>1.6699</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2735</v>
+        <v>3.075499999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.7671</v>
+        <v>-0.2191999999999998</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.5067</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.7671</v>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>play_by_play_2536317_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>G. MULERO MALDONADO</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>AMICS CASTELLÓ</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-1.593</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-4.3886</v>
-      </c>
-      <c r="F27" t="n">
-        <v>2.7957</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-2.1739</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2.061</v>
-      </c>
-      <c r="I27" t="n">
-        <v>-4.235</v>
-      </c>
-      <c r="J27" t="n">
-        <v>-3.5075</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.7104</v>
-      </c>
-      <c r="L27" t="n">
-        <v>-4.2179</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.3336</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1.3506</v>
-      </c>
-      <c r="O27" t="n">
-        <v>-0.017</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0.2055</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>-1.2329</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.4384</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0.3755</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0.3518</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0.0237</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>play_by_play_2536317_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>D. CEBOLLA PORCAR</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>AMICS CASTELLÓ</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
-        <v>-4.1001</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-5.9733</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1.8732</v>
-      </c>
-      <c r="G28" t="n">
-        <v>-3.2402</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-0.1406</v>
-      </c>
-      <c r="I28" t="n">
-        <v>-3.0997</v>
-      </c>
-      <c r="J28" t="n">
-        <v>-3.6538</v>
-      </c>
-      <c r="K28" t="n">
-        <v>-0.855</v>
-      </c>
-      <c r="L28" t="n">
-        <v>-2.7988</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.4136</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0.7145</v>
-      </c>
-      <c r="O28" t="n">
-        <v>-0.3009</v>
-      </c>
-      <c r="P28" t="n">
-        <v>-1.0274</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>-2.2603</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.2329</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0.4073</v>
-      </c>
-      <c r="T28" t="n">
-        <v>-0.0592</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0.4665</v>
-      </c>
-      <c r="V28" t="n">
-        <v>-0.2397</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>-0.2397</v>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>play_by_play_2536317_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>AMICS CASTELLÓ</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="n">
-        <v>10.6107</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-6.863799999999999</v>
-      </c>
-      <c r="F29" t="n">
-        <v>17.4748</v>
-      </c>
-      <c r="G29" t="n">
-        <v>11.2217</v>
-      </c>
-      <c r="H29" t="n">
-        <v>15.323</v>
-      </c>
-      <c r="I29" t="n">
-        <v>-4.1012</v>
-      </c>
-      <c r="J29" t="n">
-        <v>6.425699999999997</v>
-      </c>
-      <c r="K29" t="n">
-        <v>11.4632</v>
-      </c>
-      <c r="L29" t="n">
-        <v>-5.0377</v>
-      </c>
-      <c r="M29" t="n">
-        <v>4.796399999999999</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.8597</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0.9366000000000001</v>
-      </c>
-      <c r="P29" t="n">
-        <v>-5.137100000000001</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>-17.466</v>
-      </c>
-      <c r="R29" t="n">
-        <v>12.3289</v>
-      </c>
-      <c r="S29" t="n">
-        <v>4.745400000000001</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.6699</v>
-      </c>
-      <c r="U29" t="n">
-        <v>3.075499999999999</v>
-      </c>
-      <c r="V29" t="n">
-        <v>-0.2191999999999998</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.5067</v>
-      </c>
-      <c r="X29" t="n">
         <v>-2.7259</v>
       </c>
-      <c r="Y29" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
